--- a/src/src/main/webapp/portal/zkb/export/Order_History_And_Part_Order_Export.xlsx
+++ b/src/src/main/webapp/portal/zkb/export/Order_History_And_Part_Order_Export.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (2)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F3417FE-EED8-4386-8C2F-10B19D952DD8}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FF9364-8D2F-4986-965A-FD2F27EF8DA9}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="FE" sheetId="5" r:id="rId1"/>
+    <sheet name="ZKB FE" sheetId="5" r:id="rId1"/>
     <sheet name="GEFE" sheetId="4" r:id="rId2"/>
     <sheet name="ORDER HISTORY LIST" sheetId="2" r:id="rId3"/>
   </sheets>

--- a/src/src/main/webapp/portal/zkb/export/Order_History_And_Part_Order_Export.xlsx
+++ b/src/src/main/webapp/portal/zkb/export/Order_History_And_Part_Order_Export.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FF9364-8D2F-4986-965A-FD2F27EF8DA9}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08FF96F7-7409-4934-AA07-9CC8CDB179A5}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="137">
   <si>
     <t>数据类型</t>
   </si>
@@ -308,9 +308,6 @@
     <t>是否为紧急订单</t>
   </si>
   <si>
-    <t>剩余数量</t>
-  </si>
-  <si>
     <t>ZKB工程师姓名</t>
   </si>
   <si>
@@ -432,6 +429,15 @@
   </si>
   <si>
     <t>归还故障描述</t>
+  </si>
+  <si>
+    <t>备件描述</t>
+  </si>
+  <si>
+    <t>是否全新探头(代理商)</t>
+  </si>
+  <si>
+    <t>是否全新探头(400)</t>
   </si>
 </sst>
 </file>
@@ -772,18 +778,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30D46F57-3F31-4DD2-8B9D-8BBA641FDC2C}">
-  <dimension ref="A1:CE1"/>
+  <dimension ref="A1:CD1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
     <col min="2" max="2" width="25.33203125" customWidth="1"/>
-    <col min="3" max="49" width="29.33203125" customWidth="1"/>
-    <col min="50" max="53" width="33.88671875" customWidth="1"/>
-    <col min="54" max="84" width="29.33203125" customWidth="1"/>
-    <col min="85" max="85" width="33.109375" customWidth="1"/>
+    <col min="3" max="48" width="29.33203125" customWidth="1"/>
+    <col min="49" max="52" width="33.88671875" customWidth="1"/>
+    <col min="53" max="83" width="29.33203125" customWidth="1"/>
+    <col min="84" max="84" width="33.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:83" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:82" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
@@ -821,7 +827,7 @@
         <v>46</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>88</v>
@@ -830,7 +836,7 @@
         <v>10</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>89</v>
@@ -857,7 +863,7 @@
         <v>56</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>93</v>
@@ -866,7 +872,7 @@
         <v>94</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AC1" s="1" t="s">
         <v>97</v>
@@ -875,61 +881,61 @@
         <v>98</v>
       </c>
       <c r="AE1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="AG1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="AF1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="AH1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="AR1" s="1" t="s">
         <v>101</v>
       </c>
       <c r="AS1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AT1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="AT1" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="AU1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AW1" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="AX1" s="1" t="s">
         <v>104</v>
@@ -947,10 +953,10 @@
         <v>108</v>
       </c>
       <c r="BC1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="BD1" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="BE1" s="1" t="s">
         <v>110</v>
@@ -962,64 +968,64 @@
         <v>112</v>
       </c>
       <c r="BH1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="BI1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BM1" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="BJ1" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="BK1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="BL1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="BM1" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="BN1" s="1" t="s">
         <v>116</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BP1" s="1" t="s">
         <v>119</v>
       </c>
       <c r="BQ1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="BU1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="BV1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BW1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="BR1" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="BS1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="BT1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="BU1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BY1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="BW1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BZ1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="CA1" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="BY1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="BZ1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="CA1" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="CB1" s="1" t="s">
         <v>122</v>
@@ -1029,9 +1035,6 @@
       </c>
       <c r="CD1" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="CE1" s="1" t="s">
-        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1042,7 +1045,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{808C041F-1A2F-4BDE-964A-55FCAC18FF23}">
-  <dimension ref="A1:AY1"/>
+  <dimension ref="A1:AZ1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="23.21875" customWidth="1"/>
@@ -1053,12 +1056,12 @@
     <col min="10" max="19" width="24.109375" customWidth="1"/>
     <col min="20" max="21" width="35.5546875" customWidth="1"/>
     <col min="22" max="30" width="32.77734375" customWidth="1"/>
-    <col min="31" max="42" width="28.6640625" customWidth="1"/>
-    <col min="43" max="44" width="24.6640625" customWidth="1"/>
-    <col min="45" max="51" width="29.5546875" customWidth="1"/>
+    <col min="31" max="43" width="28.6640625" customWidth="1"/>
+    <col min="44" max="45" width="24.6640625" customWidth="1"/>
+    <col min="46" max="52" width="29.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:52" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
@@ -1135,19 +1138,19 @@
         <v>76</v>
       </c>
       <c r="Z1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>60</v>
@@ -1171,45 +1174,48 @@
         <v>78</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>63</v>
+        <v>135</v>
       </c>
       <c r="AM1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AN1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>82</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/zkb/export/Order_History_And_Part_Order_Export.xlsx
+++ b/src/src/main/webapp/portal/zkb/export/Order_History_And_Part_Order_Export.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08FF96F7-7409-4934-AA07-9CC8CDB179A5}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5679575C-ADF3-426C-A036-E25C621C162C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2136" yWindow="3108" windowWidth="17280" windowHeight="8976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ZKB FE" sheetId="5" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="136">
   <si>
     <t>数据类型</t>
   </si>
@@ -216,9 +216,6 @@
   </si>
   <si>
     <t>代理商审批备注</t>
-  </si>
-  <si>
-    <t>是否全新探头</t>
   </si>
   <si>
     <t>是否需要探头说明函</t>
@@ -778,18 +775,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30D46F57-3F31-4DD2-8B9D-8BBA641FDC2C}">
-  <dimension ref="A1:CD1"/>
+  <dimension ref="A1:CE1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
     <col min="2" max="2" width="25.33203125" customWidth="1"/>
-    <col min="3" max="48" width="29.33203125" customWidth="1"/>
-    <col min="49" max="52" width="33.88671875" customWidth="1"/>
-    <col min="53" max="83" width="29.33203125" customWidth="1"/>
-    <col min="84" max="84" width="33.109375" customWidth="1"/>
+    <col min="3" max="47" width="29.33203125" customWidth="1"/>
+    <col min="48" max="51" width="33.88671875" customWidth="1"/>
+    <col min="52" max="84" width="29.33203125" customWidth="1"/>
+    <col min="85" max="85" width="33.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:82" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:83" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
@@ -803,52 +800,52 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>53</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>46</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="S1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>54</v>
@@ -857,37 +854,37 @@
         <v>55</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="X1" s="1" t="s">
         <v>56</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Z1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="AA1" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="AB1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AH1" s="1" t="s">
         <v>8</v>
@@ -896,43 +893,43 @@
         <v>57</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AK1" s="1" t="s">
         <v>59</v>
       </c>
       <c r="AL1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AN1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="AO1" s="1" t="s">
-        <v>127</v>
+        <v>75</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="AQ1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AS1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AU1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="AS1" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="AW1" s="1" t="s">
         <v>103</v>
@@ -950,10 +947,10 @@
         <v>107</v>
       </c>
       <c r="BB1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="BC1" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="BD1" s="1" t="s">
         <v>109</v>
@@ -965,76 +962,79 @@
         <v>111</v>
       </c>
       <c r="BG1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="BH1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="BH1" s="1" t="s">
-        <v>114</v>
-      </c>
       <c r="BI1" s="1" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="BJ1" s="1" t="s">
         <v>77</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>52</v>
+        <v>114</v>
       </c>
       <c r="BM1" s="1" t="s">
         <v>115</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BO1" s="1" t="s">
         <v>118</v>
       </c>
       <c r="BP1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BU1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="BV1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BX1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="BQ1" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="BR1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="BS1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="BT1" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BZ1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="CA1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="BV1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="BW1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="BX1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="BY1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="BZ1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CC1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="CD1" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -1081,7 +1081,7 @@
         <v>42</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>53</v>
@@ -1114,7 +1114,7 @@
         <v>48</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>54</v>
@@ -1135,22 +1135,22 @@
         <v>59</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>60</v>
@@ -1168,55 +1168,55 @@
         <v>17</v>
       </c>
       <c r="AJ1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AS1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="AL1" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="AU1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="AV1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AW1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="AW1" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="AX1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AY1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/zkb/export/Order_History_And_Part_Order_Export.xlsx
+++ b/src/src/main/webapp/portal/zkb/export/Order_History_And_Part_Order_Export.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5679575C-ADF3-426C-A036-E25C621C162C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F66845-9A2C-4A43-8DDB-2025D49D5FE3}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2136" yWindow="3108" windowWidth="17280" windowHeight="8976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ZKB FE" sheetId="5" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="136">
   <si>
     <t>数据类型</t>
   </si>
@@ -775,18 +775,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30D46F57-3F31-4DD2-8B9D-8BBA641FDC2C}">
-  <dimension ref="A1:CE1"/>
+  <dimension ref="A1:CD1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
     <col min="2" max="2" width="25.33203125" customWidth="1"/>
     <col min="3" max="47" width="29.33203125" customWidth="1"/>
     <col min="48" max="51" width="33.88671875" customWidth="1"/>
-    <col min="52" max="84" width="29.33203125" customWidth="1"/>
-    <col min="85" max="85" width="33.109375" customWidth="1"/>
+    <col min="52" max="83" width="29.33203125" customWidth="1"/>
+    <col min="84" max="84" width="33.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:83" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:82" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>41</v>
       </c>
@@ -1019,21 +1019,18 @@
         <v>70</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="CE1" s="1" t="s">
         <v>123</v>
       </c>
     </row>
